--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119928370</v>
+        <v>119929028</v>
       </c>
       <c r="B10" t="n">
-        <v>78262</v>
+        <v>91884</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712192</v>
+        <v>712151</v>
       </c>
       <c r="R10" t="n">
-        <v>7301729</v>
+        <v>7301954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119929028</v>
+        <v>119928370</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>78262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712151</v>
+        <v>712192</v>
       </c>
       <c r="R11" t="n">
-        <v>7301954</v>
+        <v>7301729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928686</v>
+        <v>119928370</v>
       </c>
       <c r="B2" t="n">
-        <v>89252</v>
+        <v>78262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712226</v>
+        <v>712192</v>
       </c>
       <c r="R2" t="n">
-        <v>7301719</v>
+        <v>7301729</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928917</v>
+        <v>119929012</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712226</v>
+        <v>712281</v>
       </c>
       <c r="R3" t="n">
-        <v>7301719</v>
+        <v>7301980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119928996</v>
+        <v>119928686</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712250</v>
+        <v>712226</v>
       </c>
       <c r="R4" t="n">
-        <v>7301747</v>
+        <v>7301719</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119929023</v>
+        <v>119928917</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712198</v>
+        <v>712226</v>
       </c>
       <c r="R5" t="n">
-        <v>7301945</v>
+        <v>7301719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119928037</v>
+        <v>119928178</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
+        <v>78262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712024</v>
+        <v>712083</v>
       </c>
       <c r="R6" t="n">
-        <v>7301839</v>
+        <v>7301768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928404</v>
+        <v>119928037</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>82305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712195</v>
+        <v>712024</v>
       </c>
       <c r="R7" t="n">
-        <v>7301722</v>
+        <v>7301839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119929007</v>
+        <v>119929095</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712426</v>
+        <v>712107</v>
       </c>
       <c r="R8" t="n">
-        <v>7301779</v>
+        <v>7301941</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119929095</v>
+        <v>119928996</v>
       </c>
       <c r="B9" t="n">
         <v>91884</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712107</v>
+        <v>712250</v>
       </c>
       <c r="R9" t="n">
-        <v>7301941</v>
+        <v>7301747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119929028</v>
+        <v>119928404</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712151</v>
+        <v>712195</v>
       </c>
       <c r="R10" t="n">
-        <v>7301954</v>
+        <v>7301722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119928370</v>
+        <v>119929007</v>
       </c>
       <c r="B11" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712192</v>
+        <v>712426</v>
       </c>
       <c r="R11" t="n">
-        <v>7301729</v>
+        <v>7301779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119928353</v>
+        <v>119929023</v>
       </c>
       <c r="B12" t="n">
-        <v>82305</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712089</v>
+        <v>712198</v>
       </c>
       <c r="R12" t="n">
-        <v>7301760</v>
+        <v>7301945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119929012</v>
+        <v>119928353</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>82305</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712281</v>
+        <v>712089</v>
       </c>
       <c r="R13" t="n">
-        <v>7301980</v>
+        <v>7301760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119928045</v>
+        <v>119929028</v>
       </c>
       <c r="B14" t="n">
-        <v>78263</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712065</v>
+        <v>712151</v>
       </c>
       <c r="R14" t="n">
-        <v>7301797</v>
+        <v>7301954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119928178</v>
+        <v>119928045</v>
       </c>
       <c r="B15" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712083</v>
+        <v>712065</v>
       </c>
       <c r="R15" t="n">
-        <v>7301768</v>
+        <v>7301797</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928370</v>
+        <v>119928353</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>82305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712192</v>
+        <v>712089</v>
       </c>
       <c r="R2" t="n">
-        <v>7301729</v>
+        <v>7301760</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119929012</v>
+        <v>119928178</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712281</v>
+        <v>712083</v>
       </c>
       <c r="R3" t="n">
-        <v>7301980</v>
+        <v>7301768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119928686</v>
+        <v>119929007</v>
       </c>
       <c r="B4" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712226</v>
+        <v>712426</v>
       </c>
       <c r="R4" t="n">
-        <v>7301719</v>
+        <v>7301779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928917</v>
+        <v>119928037</v>
       </c>
       <c r="B5" t="n">
-        <v>91856</v>
+        <v>82305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712226</v>
+        <v>712024</v>
       </c>
       <c r="R5" t="n">
-        <v>7301719</v>
+        <v>7301839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119928178</v>
+        <v>119928686</v>
       </c>
       <c r="B6" t="n">
-        <v>78262</v>
+        <v>89252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712083</v>
+        <v>712226</v>
       </c>
       <c r="R6" t="n">
-        <v>7301768</v>
+        <v>7301719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928037</v>
+        <v>119928045</v>
       </c>
       <c r="B7" t="n">
-        <v>82305</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712024</v>
+        <v>712065</v>
       </c>
       <c r="R7" t="n">
-        <v>7301839</v>
+        <v>7301797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119928996</v>
+        <v>119928917</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712250</v>
+        <v>712226</v>
       </c>
       <c r="R9" t="n">
-        <v>7301747</v>
+        <v>7301719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119928404</v>
+        <v>119928996</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712195</v>
+        <v>712250</v>
       </c>
       <c r="R10" t="n">
-        <v>7301722</v>
+        <v>7301747</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119929007</v>
+        <v>119928404</v>
       </c>
       <c r="B11" t="n">
         <v>91840</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712426</v>
+        <v>712195</v>
       </c>
       <c r="R11" t="n">
-        <v>7301779</v>
+        <v>7301722</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119929023</v>
+        <v>119929028</v>
       </c>
       <c r="B12" t="n">
         <v>91884</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712198</v>
+        <v>712151</v>
       </c>
       <c r="R12" t="n">
-        <v>7301945</v>
+        <v>7301954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119928353</v>
+        <v>119929012</v>
       </c>
       <c r="B13" t="n">
-        <v>82305</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712089</v>
+        <v>712281</v>
       </c>
       <c r="R13" t="n">
-        <v>7301760</v>
+        <v>7301980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119929028</v>
+        <v>119928370</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>78262</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712151</v>
+        <v>712192</v>
       </c>
       <c r="R14" t="n">
-        <v>7301954</v>
+        <v>7301729</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119928045</v>
+        <v>119929023</v>
       </c>
       <c r="B15" t="n">
-        <v>78263</v>
+        <v>91884</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712065</v>
+        <v>712198</v>
       </c>
       <c r="R15" t="n">
-        <v>7301797</v>
+        <v>7301945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119928686</v>
+        <v>119928045</v>
       </c>
       <c r="B6" t="n">
-        <v>89252</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712226</v>
+        <v>712065</v>
       </c>
       <c r="R6" t="n">
-        <v>7301719</v>
+        <v>7301797</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928045</v>
+        <v>119928686</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>89252</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712065</v>
+        <v>712226</v>
       </c>
       <c r="R7" t="n">
-        <v>7301797</v>
+        <v>7301719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928353</v>
+        <v>119929007</v>
       </c>
       <c r="B2" t="n">
-        <v>82305</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712089</v>
+        <v>712426</v>
       </c>
       <c r="R2" t="n">
-        <v>7301760</v>
+        <v>7301779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928178</v>
+        <v>119928404</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712083</v>
+        <v>712195</v>
       </c>
       <c r="R3" t="n">
-        <v>7301768</v>
+        <v>7301722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119929007</v>
+        <v>119929012</v>
       </c>
       <c r="B4" t="n">
         <v>91840</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712426</v>
+        <v>712281</v>
       </c>
       <c r="R4" t="n">
-        <v>7301779</v>
+        <v>7301980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928037</v>
+        <v>119928045</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712024</v>
+        <v>712065</v>
       </c>
       <c r="R5" t="n">
-        <v>7301839</v>
+        <v>7301797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119928045</v>
+        <v>119928370</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712065</v>
+        <v>712192</v>
       </c>
       <c r="R6" t="n">
-        <v>7301797</v>
+        <v>7301729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928686</v>
+        <v>119928178</v>
       </c>
       <c r="B7" t="n">
-        <v>89252</v>
+        <v>78262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712226</v>
+        <v>712083</v>
       </c>
       <c r="R7" t="n">
-        <v>7301719</v>
+        <v>7301768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119928404</v>
+        <v>119929028</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712195</v>
+        <v>712151</v>
       </c>
       <c r="R11" t="n">
-        <v>7301722</v>
+        <v>7301954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119929028</v>
+        <v>119928037</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>82305</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712151</v>
+        <v>712024</v>
       </c>
       <c r="R12" t="n">
-        <v>7301954</v>
+        <v>7301839</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119929012</v>
+        <v>119929023</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712281</v>
+        <v>712198</v>
       </c>
       <c r="R13" t="n">
-        <v>7301980</v>
+        <v>7301945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119928370</v>
+        <v>119928686</v>
       </c>
       <c r="B14" t="n">
-        <v>78262</v>
+        <v>89252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712192</v>
+        <v>712226</v>
       </c>
       <c r="R14" t="n">
-        <v>7301729</v>
+        <v>7301719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119929023</v>
+        <v>119928353</v>
       </c>
       <c r="B15" t="n">
-        <v>91884</v>
+        <v>82305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712198</v>
+        <v>712089</v>
       </c>
       <c r="R15" t="n">
-        <v>7301945</v>
+        <v>7301760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119928686</v>
+        <v>119928353</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
+        <v>82305</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712226</v>
+        <v>712089</v>
       </c>
       <c r="R14" t="n">
-        <v>7301719</v>
+        <v>7301760</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119928353</v>
+        <v>119928686</v>
       </c>
       <c r="B15" t="n">
-        <v>82305</v>
+        <v>89252</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712089</v>
+        <v>712226</v>
       </c>
       <c r="R15" t="n">
-        <v>7301760</v>
+        <v>7301719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119928353</v>
+        <v>119928686</v>
       </c>
       <c r="B14" t="n">
-        <v>82305</v>
+        <v>89252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712089</v>
+        <v>712226</v>
       </c>
       <c r="R14" t="n">
-        <v>7301760</v>
+        <v>7301719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119928686</v>
+        <v>119928353</v>
       </c>
       <c r="B15" t="n">
-        <v>89252</v>
+        <v>82305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712226</v>
+        <v>712089</v>
       </c>
       <c r="R15" t="n">
-        <v>7301719</v>
+        <v>7301760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119929007</v>
+        <v>119928686</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>89269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712426</v>
+        <v>712226</v>
       </c>
       <c r="R2" t="n">
-        <v>7301779</v>
+        <v>7301719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928404</v>
+        <v>119928917</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712195</v>
+        <v>712226</v>
       </c>
       <c r="R3" t="n">
-        <v>7301722</v>
+        <v>7301719</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119929012</v>
+        <v>119928037</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712281</v>
+        <v>712024</v>
       </c>
       <c r="R4" t="n">
-        <v>7301980</v>
+        <v>7301839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928045</v>
+        <v>119928178</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712065</v>
+        <v>712083</v>
       </c>
       <c r="R5" t="n">
-        <v>7301797</v>
+        <v>7301768</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119928370</v>
+        <v>119929028</v>
       </c>
       <c r="B6" t="n">
-        <v>78262</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712192</v>
+        <v>712151</v>
       </c>
       <c r="R6" t="n">
-        <v>7301729</v>
+        <v>7301954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928178</v>
+        <v>119929007</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712083</v>
+        <v>712426</v>
       </c>
       <c r="R7" t="n">
-        <v>7301768</v>
+        <v>7301779</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119929095</v>
+        <v>119928353</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712107</v>
+        <v>712089</v>
       </c>
       <c r="R8" t="n">
-        <v>7301941</v>
+        <v>7301760</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119928917</v>
+        <v>119929012</v>
       </c>
       <c r="B9" t="n">
-        <v>91856</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712226</v>
+        <v>712281</v>
       </c>
       <c r="R9" t="n">
-        <v>7301719</v>
+        <v>7301980</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
         <v>119928996</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119929028</v>
+        <v>119929023</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712151</v>
+        <v>712198</v>
       </c>
       <c r="R11" t="n">
-        <v>7301954</v>
+        <v>7301945</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119928037</v>
+        <v>119928045</v>
       </c>
       <c r="B12" t="n">
-        <v>82305</v>
+        <v>78279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712024</v>
+        <v>712065</v>
       </c>
       <c r="R12" t="n">
-        <v>7301839</v>
+        <v>7301797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119929023</v>
+        <v>119929095</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712198</v>
+        <v>712107</v>
       </c>
       <c r="R13" t="n">
-        <v>7301945</v>
+        <v>7301941</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119928686</v>
+        <v>119928370</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712226</v>
+        <v>712192</v>
       </c>
       <c r="R14" t="n">
-        <v>7301719</v>
+        <v>7301729</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119928353</v>
+        <v>119928404</v>
       </c>
       <c r="B15" t="n">
-        <v>82305</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712089</v>
+        <v>712195</v>
       </c>
       <c r="R15" t="n">
-        <v>7301760</v>
+        <v>7301722</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928917</v>
+        <v>119928037</v>
       </c>
       <c r="B3" t="n">
-        <v>91874</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712226</v>
+        <v>712024</v>
       </c>
       <c r="R3" t="n">
-        <v>7301719</v>
+        <v>7301839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119928037</v>
+        <v>119928178</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712024</v>
+        <v>712083</v>
       </c>
       <c r="R4" t="n">
-        <v>7301839</v>
+        <v>7301768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928178</v>
+        <v>119928917</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>91874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712083</v>
+        <v>712226</v>
       </c>
       <c r="R5" t="n">
-        <v>7301768</v>
+        <v>7301719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928686</v>
+        <v>119928178</v>
       </c>
       <c r="B2" t="n">
-        <v>89269</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712226</v>
+        <v>712083</v>
       </c>
       <c r="R2" t="n">
-        <v>7301719</v>
+        <v>7301768</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928037</v>
+        <v>119928370</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712024</v>
+        <v>712192</v>
       </c>
       <c r="R3" t="n">
-        <v>7301839</v>
+        <v>7301729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119928178</v>
+        <v>119928353</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712083</v>
+        <v>712089</v>
       </c>
       <c r="R4" t="n">
-        <v>7301768</v>
+        <v>7301760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928917</v>
+        <v>119928045</v>
       </c>
       <c r="B5" t="n">
-        <v>91874</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712226</v>
+        <v>712065</v>
       </c>
       <c r="R5" t="n">
-        <v>7301719</v>
+        <v>7301797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119929028</v>
+        <v>119929012</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712151</v>
+        <v>712281</v>
       </c>
       <c r="R6" t="n">
-        <v>7301954</v>
+        <v>7301980</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119929007</v>
+        <v>119928404</v>
       </c>
       <c r="B7" t="n">
         <v>91858</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712426</v>
+        <v>712195</v>
       </c>
       <c r="R7" t="n">
-        <v>7301779</v>
+        <v>7301722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119928353</v>
+        <v>119928686</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>89269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712089</v>
+        <v>712226</v>
       </c>
       <c r="R8" t="n">
-        <v>7301760</v>
+        <v>7301719</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119929012</v>
+        <v>119929023</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712281</v>
+        <v>712198</v>
       </c>
       <c r="R9" t="n">
-        <v>7301980</v>
+        <v>7301945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119928996</v>
+        <v>119929028</v>
       </c>
       <c r="B10" t="n">
         <v>91902</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712250</v>
+        <v>712151</v>
       </c>
       <c r="R10" t="n">
-        <v>7301747</v>
+        <v>7301954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119929023</v>
+        <v>119928996</v>
       </c>
       <c r="B11" t="n">
         <v>91902</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712198</v>
+        <v>712250</v>
       </c>
       <c r="R11" t="n">
-        <v>7301945</v>
+        <v>7301747</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119928045</v>
+        <v>119928917</v>
       </c>
       <c r="B12" t="n">
-        <v>78279</v>
+        <v>91874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712065</v>
+        <v>712226</v>
       </c>
       <c r="R12" t="n">
-        <v>7301797</v>
+        <v>7301719</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119929095</v>
+        <v>119929007</v>
       </c>
       <c r="B13" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712107</v>
+        <v>712426</v>
       </c>
       <c r="R13" t="n">
-        <v>7301941</v>
+        <v>7301779</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119928370</v>
+        <v>119928037</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>82321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712192</v>
+        <v>712024</v>
       </c>
       <c r="R14" t="n">
-        <v>7301729</v>
+        <v>7301839</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119928404</v>
+        <v>119929095</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712195</v>
+        <v>712107</v>
       </c>
       <c r="R15" t="n">
-        <v>7301722</v>
+        <v>7301941</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928178</v>
+        <v>119929095</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712083</v>
+        <v>712107</v>
       </c>
       <c r="R2" t="n">
-        <v>7301768</v>
+        <v>7301941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928370</v>
+        <v>119928917</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>91874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712192</v>
+        <v>712226</v>
       </c>
       <c r="R3" t="n">
-        <v>7301729</v>
+        <v>7301719</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119928353</v>
+        <v>119928996</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712089</v>
+        <v>712250</v>
       </c>
       <c r="R4" t="n">
-        <v>7301760</v>
+        <v>7301747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119929012</v>
+        <v>119928178</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712281</v>
+        <v>712083</v>
       </c>
       <c r="R6" t="n">
-        <v>7301980</v>
+        <v>7301768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928404</v>
+        <v>119928686</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712195</v>
+        <v>712226</v>
       </c>
       <c r="R7" t="n">
-        <v>7301722</v>
+        <v>7301719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119928686</v>
+        <v>119929028</v>
       </c>
       <c r="B8" t="n">
-        <v>89269</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712226</v>
+        <v>712151</v>
       </c>
       <c r="R8" t="n">
-        <v>7301719</v>
+        <v>7301954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119929023</v>
+        <v>119929012</v>
       </c>
       <c r="B9" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712198</v>
+        <v>712281</v>
       </c>
       <c r="R9" t="n">
-        <v>7301945</v>
+        <v>7301980</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119929028</v>
+        <v>119928404</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712151</v>
+        <v>712195</v>
       </c>
       <c r="R10" t="n">
-        <v>7301954</v>
+        <v>7301722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119928996</v>
+        <v>119928037</v>
       </c>
       <c r="B11" t="n">
-        <v>91902</v>
+        <v>82321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712250</v>
+        <v>712024</v>
       </c>
       <c r="R11" t="n">
-        <v>7301747</v>
+        <v>7301839</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119928917</v>
+        <v>119928370</v>
       </c>
       <c r="B12" t="n">
-        <v>91874</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712226</v>
+        <v>712192</v>
       </c>
       <c r="R12" t="n">
-        <v>7301719</v>
+        <v>7301729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119928037</v>
+        <v>119929023</v>
       </c>
       <c r="B14" t="n">
-        <v>82321</v>
+        <v>91902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712024</v>
+        <v>712198</v>
       </c>
       <c r="R14" t="n">
-        <v>7301839</v>
+        <v>7301945</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119929095</v>
+        <v>119928353</v>
       </c>
       <c r="B15" t="n">
-        <v>91902</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712107</v>
+        <v>712089</v>
       </c>
       <c r="R15" t="n">
-        <v>7301941</v>
+        <v>7301760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928686</v>
+        <v>119929028</v>
       </c>
       <c r="B7" t="n">
-        <v>89269</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712226</v>
+        <v>712151</v>
       </c>
       <c r="R7" t="n">
-        <v>7301719</v>
+        <v>7301954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119929028</v>
+        <v>119928686</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
+        <v>89269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712151</v>
+        <v>712226</v>
       </c>
       <c r="R8" t="n">
-        <v>7301954</v>
+        <v>7301719</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119929023</v>
+        <v>119928353</v>
       </c>
       <c r="B14" t="n">
-        <v>91902</v>
+        <v>82321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712198</v>
+        <v>712089</v>
       </c>
       <c r="R14" t="n">
-        <v>7301945</v>
+        <v>7301760</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119928353</v>
+        <v>119929023</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>91902</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712089</v>
+        <v>712198</v>
       </c>
       <c r="R15" t="n">
-        <v>7301760</v>
+        <v>7301945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119929095</v>
+        <v>119928404</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712107</v>
+        <v>712195</v>
       </c>
       <c r="R2" t="n">
-        <v>7301941</v>
+        <v>7301722</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928917</v>
+        <v>119928370</v>
       </c>
       <c r="B3" t="n">
-        <v>91874</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712226</v>
+        <v>712192</v>
       </c>
       <c r="R3" t="n">
-        <v>7301719</v>
+        <v>7301729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119928996</v>
+        <v>119929023</v>
       </c>
       <c r="B4" t="n">
         <v>91902</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712250</v>
+        <v>712198</v>
       </c>
       <c r="R4" t="n">
-        <v>7301747</v>
+        <v>7301945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928045</v>
+        <v>119928917</v>
       </c>
       <c r="B5" t="n">
-        <v>78279</v>
+        <v>91874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712065</v>
+        <v>712226</v>
       </c>
       <c r="R5" t="n">
-        <v>7301797</v>
+        <v>7301719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119928178</v>
+        <v>119928045</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712083</v>
+        <v>712065</v>
       </c>
       <c r="R6" t="n">
-        <v>7301768</v>
+        <v>7301797</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119929028</v>
+        <v>119928996</v>
       </c>
       <c r="B7" t="n">
         <v>91902</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712151</v>
+        <v>712250</v>
       </c>
       <c r="R7" t="n">
-        <v>7301954</v>
+        <v>7301747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119928686</v>
+        <v>119929028</v>
       </c>
       <c r="B8" t="n">
-        <v>89269</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712226</v>
+        <v>712151</v>
       </c>
       <c r="R8" t="n">
-        <v>7301719</v>
+        <v>7301954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119929012</v>
+        <v>119928178</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712281</v>
+        <v>712083</v>
       </c>
       <c r="R9" t="n">
-        <v>7301980</v>
+        <v>7301768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119928404</v>
+        <v>119928686</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712195</v>
+        <v>712226</v>
       </c>
       <c r="R10" t="n">
-        <v>7301722</v>
+        <v>7301719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119928037</v>
+        <v>119929012</v>
       </c>
       <c r="B11" t="n">
-        <v>82321</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712024</v>
+        <v>712281</v>
       </c>
       <c r="R11" t="n">
-        <v>7301839</v>
+        <v>7301980</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119928370</v>
+        <v>119928353</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712192</v>
+        <v>712089</v>
       </c>
       <c r="R12" t="n">
-        <v>7301729</v>
+        <v>7301760</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119929007</v>
+        <v>119928037</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712426</v>
+        <v>712024</v>
       </c>
       <c r="R13" t="n">
-        <v>7301779</v>
+        <v>7301839</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119928353</v>
+        <v>119929095</v>
       </c>
       <c r="B14" t="n">
-        <v>82321</v>
+        <v>91902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712089</v>
+        <v>712107</v>
       </c>
       <c r="R14" t="n">
-        <v>7301760</v>
+        <v>7301941</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119929023</v>
+        <v>119929007</v>
       </c>
       <c r="B15" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712198</v>
+        <v>712426</v>
       </c>
       <c r="R15" t="n">
-        <v>7301945</v>
+        <v>7301779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928404</v>
+        <v>119928996</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712195</v>
+        <v>712250</v>
       </c>
       <c r="R2" t="n">
-        <v>7301722</v>
+        <v>7301747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928370</v>
+        <v>119928917</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>91874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712192</v>
+        <v>712226</v>
       </c>
       <c r="R3" t="n">
-        <v>7301729</v>
+        <v>7301719</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119929023</v>
+        <v>119928045</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712198</v>
+        <v>712065</v>
       </c>
       <c r="R4" t="n">
-        <v>7301945</v>
+        <v>7301797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928917</v>
+        <v>119928353</v>
       </c>
       <c r="B5" t="n">
-        <v>91874</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712226</v>
+        <v>712089</v>
       </c>
       <c r="R5" t="n">
-        <v>7301719</v>
+        <v>7301760</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119928045</v>
+        <v>119929095</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712065</v>
+        <v>712107</v>
       </c>
       <c r="R6" t="n">
-        <v>7301797</v>
+        <v>7301941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928996</v>
+        <v>119928686</v>
       </c>
       <c r="B7" t="n">
-        <v>91902</v>
+        <v>89269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712250</v>
+        <v>712226</v>
       </c>
       <c r="R7" t="n">
-        <v>7301747</v>
+        <v>7301719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119929028</v>
+        <v>119929007</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712151</v>
+        <v>712426</v>
       </c>
       <c r="R8" t="n">
-        <v>7301954</v>
+        <v>7301779</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119928178</v>
+        <v>119928037</v>
       </c>
       <c r="B9" t="n">
-        <v>78278</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712083</v>
+        <v>712024</v>
       </c>
       <c r="R9" t="n">
-        <v>7301768</v>
+        <v>7301839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119928686</v>
+        <v>119928370</v>
       </c>
       <c r="B10" t="n">
-        <v>89269</v>
+        <v>78278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712226</v>
+        <v>712192</v>
       </c>
       <c r="R10" t="n">
-        <v>7301719</v>
+        <v>7301729</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119929012</v>
+        <v>119928178</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712281</v>
+        <v>712083</v>
       </c>
       <c r="R11" t="n">
-        <v>7301980</v>
+        <v>7301768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119928353</v>
+        <v>119928404</v>
       </c>
       <c r="B12" t="n">
-        <v>82321</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712089</v>
+        <v>712195</v>
       </c>
       <c r="R12" t="n">
-        <v>7301760</v>
+        <v>7301722</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119928037</v>
+        <v>119929023</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>91902</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712024</v>
+        <v>712198</v>
       </c>
       <c r="R13" t="n">
-        <v>7301839</v>
+        <v>7301945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119929095</v>
+        <v>119929012</v>
       </c>
       <c r="B14" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712107</v>
+        <v>712281</v>
       </c>
       <c r="R14" t="n">
-        <v>7301941</v>
+        <v>7301980</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119929007</v>
+        <v>119929028</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712426</v>
+        <v>712151</v>
       </c>
       <c r="R15" t="n">
-        <v>7301779</v>
+        <v>7301954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928996</v>
+        <v>119928917</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712250</v>
+        <v>712226</v>
       </c>
       <c r="R2" t="n">
-        <v>7301747</v>
+        <v>7301719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928917</v>
+        <v>119928996</v>
       </c>
       <c r="B3" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712226</v>
+        <v>712250</v>
       </c>
       <c r="R3" t="n">
-        <v>7301719</v>
+        <v>7301747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119928045</v>
+        <v>119928353</v>
       </c>
       <c r="B4" t="n">
-        <v>78279</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712065</v>
+        <v>712089</v>
       </c>
       <c r="R4" t="n">
-        <v>7301797</v>
+        <v>7301760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928353</v>
+        <v>119928045</v>
       </c>
       <c r="B5" t="n">
-        <v>82321</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712089</v>
+        <v>712065</v>
       </c>
       <c r="R5" t="n">
-        <v>7301760</v>
+        <v>7301797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119929007</v>
+        <v>119928037</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712426</v>
+        <v>712024</v>
       </c>
       <c r="R8" t="n">
-        <v>7301779</v>
+        <v>7301839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119928037</v>
+        <v>119929007</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712024</v>
+        <v>712426</v>
       </c>
       <c r="R9" t="n">
-        <v>7301839</v>
+        <v>7301779</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928917</v>
+        <v>119928996</v>
       </c>
       <c r="B2" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712226</v>
+        <v>712250</v>
       </c>
       <c r="R2" t="n">
-        <v>7301719</v>
+        <v>7301747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928996</v>
+        <v>119928353</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712250</v>
+        <v>712089</v>
       </c>
       <c r="R3" t="n">
-        <v>7301747</v>
+        <v>7301760</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119928353</v>
+        <v>119928037</v>
       </c>
       <c r="B4" t="n">
         <v>82321</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712089</v>
+        <v>712024</v>
       </c>
       <c r="R4" t="n">
-        <v>7301760</v>
+        <v>7301839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119928045</v>
+        <v>119929095</v>
       </c>
       <c r="B5" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712065</v>
+        <v>712107</v>
       </c>
       <c r="R5" t="n">
-        <v>7301797</v>
+        <v>7301941</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119929095</v>
+        <v>119929028</v>
       </c>
       <c r="B6" t="n">
         <v>91902</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712107</v>
+        <v>712151</v>
       </c>
       <c r="R6" t="n">
-        <v>7301941</v>
+        <v>7301954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928686</v>
+        <v>119928917</v>
       </c>
       <c r="B7" t="n">
-        <v>89269</v>
+        <v>91874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119928037</v>
+        <v>119928370</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712024</v>
+        <v>712192</v>
       </c>
       <c r="R8" t="n">
-        <v>7301839</v>
+        <v>7301729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119929007</v>
+        <v>119929023</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712426</v>
+        <v>712198</v>
       </c>
       <c r="R9" t="n">
-        <v>7301779</v>
+        <v>7301945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119928370</v>
+        <v>119928686</v>
       </c>
       <c r="B10" t="n">
-        <v>78278</v>
+        <v>89269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712192</v>
+        <v>712226</v>
       </c>
       <c r="R10" t="n">
-        <v>7301729</v>
+        <v>7301719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119928404</v>
+        <v>119929007</v>
       </c>
       <c r="B12" t="n">
         <v>91858</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712195</v>
+        <v>712426</v>
       </c>
       <c r="R12" t="n">
-        <v>7301722</v>
+        <v>7301779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119929023</v>
+        <v>119928045</v>
       </c>
       <c r="B13" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712198</v>
+        <v>712065</v>
       </c>
       <c r="R13" t="n">
-        <v>7301945</v>
+        <v>7301797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119929028</v>
+        <v>119928404</v>
       </c>
       <c r="B15" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712151</v>
+        <v>712195</v>
       </c>
       <c r="R15" t="n">
-        <v>7301954</v>
+        <v>7301722</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 37507-2024 artfynd.xlsx
+++ b/artfynd/A 37507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119928996</v>
+        <v>119928045</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712250</v>
+        <v>712065</v>
       </c>
       <c r="R2" t="n">
-        <v>7301747</v>
+        <v>7301797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119928353</v>
+        <v>119929012</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712089</v>
+        <v>712281</v>
       </c>
       <c r="R3" t="n">
-        <v>7301760</v>
+        <v>7301980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119929095</v>
+        <v>119928404</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712107</v>
+        <v>712195</v>
       </c>
       <c r="R5" t="n">
-        <v>7301941</v>
+        <v>7301722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119929028</v>
+        <v>119929023</v>
       </c>
       <c r="B6" t="n">
         <v>91902</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712151</v>
+        <v>712198</v>
       </c>
       <c r="R6" t="n">
-        <v>7301954</v>
+        <v>7301945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119928917</v>
+        <v>119929007</v>
       </c>
       <c r="B7" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712226</v>
+        <v>712426</v>
       </c>
       <c r="R7" t="n">
-        <v>7301719</v>
+        <v>7301779</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119928370</v>
+        <v>119928686</v>
       </c>
       <c r="B8" t="n">
-        <v>78278</v>
+        <v>89269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712192</v>
+        <v>712226</v>
       </c>
       <c r="R8" t="n">
-        <v>7301729</v>
+        <v>7301719</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119929023</v>
+        <v>119929028</v>
       </c>
       <c r="B9" t="n">
         <v>91902</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712198</v>
+        <v>712151</v>
       </c>
       <c r="R9" t="n">
-        <v>7301945</v>
+        <v>7301954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119928686</v>
+        <v>119928353</v>
       </c>
       <c r="B10" t="n">
-        <v>89269</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712226</v>
+        <v>712089</v>
       </c>
       <c r="R10" t="n">
-        <v>7301719</v>
+        <v>7301760</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119928178</v>
+        <v>119929095</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>91902</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712083</v>
+        <v>712107</v>
       </c>
       <c r="R11" t="n">
-        <v>7301768</v>
+        <v>7301941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119929007</v>
+        <v>119928917</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712426</v>
+        <v>712226</v>
       </c>
       <c r="R12" t="n">
-        <v>7301779</v>
+        <v>7301719</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119928045</v>
+        <v>119928996</v>
       </c>
       <c r="B13" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712065</v>
+        <v>712250</v>
       </c>
       <c r="R13" t="n">
-        <v>7301797</v>
+        <v>7301747</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119929012</v>
+        <v>119928178</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712281</v>
+        <v>712083</v>
       </c>
       <c r="R14" t="n">
-        <v>7301980</v>
+        <v>7301768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119928404</v>
+        <v>119928370</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712195</v>
+        <v>712192</v>
       </c>
       <c r="R15" t="n">
-        <v>7301722</v>
+        <v>7301729</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
